--- a/02_clean_data/46_09_Models3_aic.xlsx
+++ b/02_clean_data/46_09_Models3_aic.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\recup\Desktop\TESIS\PAPERS\01_INDIVIDUO\git_repo\Tesis_Individuo\02_clean_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114DBDF2-466C-4260-97D9-034E9CD90CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -182,11 +190,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,7 +213,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -213,19 +228,327 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -242,507 +565,507 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
-        <v>2.49836842801005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4.05554023593737</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2" s="1">
+        <v>2.4983684280100502</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.0555402359373698</v>
+      </c>
+      <c r="E2">
         <v>-1.61398168161759</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.952872101426181</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2">
+        <v>-0.95287210142618095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="n">
-        <v>1.69472763950307</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.04174811635244</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.99416587482949</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="C3">
+        <v>1.6947276395030699</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.0417481163524398</v>
+      </c>
+      <c r="E3">
+        <v>-1.9941658748294899</v>
+      </c>
+      <c r="F3">
         <v>-1.03902722010798</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="n">
-        <v>-1.51678051238355</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.24403702443749</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="C4">
+        <v>-1.5167805123835501</v>
+      </c>
+      <c r="D4">
+        <v>-1.2440370244374901</v>
+      </c>
+      <c r="E4">
         <v>-1.24131963378295</v>
       </c>
-      <c r="F4" t="n">
-        <v>-0.306760521630395</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4">
+        <v>-0.30676052163039502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1">
         <v>4.98401170080888</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>-1.11061784884583</v>
       </c>
-      <c r="E5" t="n">
-        <v>5.08133332436955</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1.50611162372519</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5" s="1">
+        <v>5.0813333243695498</v>
+      </c>
+      <c r="F5">
+        <v>-1.5061116237251899</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="n">
-        <v>-1.87218358416169</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>-1.8721835841616901</v>
+      </c>
+      <c r="D6">
         <v>-1.7553614693463</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-1.98677763236105</v>
       </c>
-      <c r="F6" t="n">
-        <v>-1.75515301551007</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="F6">
+        <v>-1.7551530155100701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1.12444723456513</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>-1.43049892727155</v>
       </c>
-      <c r="E7" t="n">
-        <v>-0.403811071890487</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.342989940794851</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="E7">
+        <v>-0.40381107189048698</v>
+      </c>
+      <c r="F7">
+        <v>0.34298994079485101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1">
         <v>2.58185195037413</v>
       </c>
-      <c r="D8" t="n">
-        <v>-1.80353407450872</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0448659162402691</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.384826349612354</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="D8">
+        <v>-1.8035340745087201</v>
+      </c>
+      <c r="E8">
+        <v>4.4865916240269102E-2</v>
+      </c>
+      <c r="F8">
+        <v>0.38482634961235401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>-0.637254820761882</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.889985782025576</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-1.95332686508345</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.47187084286151</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="D9">
+        <v>0.88998578202557599</v>
+      </c>
+      <c r="E9">
+        <v>-1.9533268650834501</v>
+      </c>
+      <c r="F9">
+        <v>-1.4718708428615099</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1">
         <v>13.5657157077771</v>
       </c>
-      <c r="D10" t="n">
-        <v>9.51035311133199</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7.14364291675588</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.902764589247681</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="D10" s="1">
+        <v>9.5103531113319892</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7.1436429167558799</v>
+      </c>
+      <c r="F10">
+        <v>-0.90276458924768099</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="n">
-        <v>5.01905556629436</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="1">
+        <v>5.0190555662943597</v>
+      </c>
+      <c r="D11">
         <v>-1.99621313693694</v>
       </c>
-      <c r="E11" t="n">
-        <v>4.37266795588698</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.06604771829052</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11" s="1">
+        <v>4.3726679558869801</v>
+      </c>
+      <c r="F11" s="1">
+        <v>6.0660477182905197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="n">
-        <v>2.45088535606283</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="1">
+        <v>2.4508853560628299</v>
+      </c>
+      <c r="D12">
         <v>-1.94581988097832</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.666710489024354</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6.63875706136548</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12">
+        <v>0.66671048902435404</v>
+      </c>
+      <c r="F12" s="1">
+        <v>6.6387570613654798</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="n">
-        <v>4.60197801857612</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.98852507591221</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3.35714980248531</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6.53812993138786</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="C13" s="1">
+        <v>4.6019780185761201</v>
+      </c>
+      <c r="D13">
+        <v>-1.9885250759122099</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3.3571498024853099</v>
+      </c>
+      <c r="F13" s="1">
+        <v>6.5381299313878598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.607919922562132</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14">
+        <v>0.60791992256213201</v>
+      </c>
+      <c r="D14">
         <v>-1.96320821084799</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.643386074729165</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14">
+        <v>0.64338607472916498</v>
+      </c>
+      <c r="F14">
         <v>1.4073434874752</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>1.72964613017159</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>-1.93496572693978</v>
       </c>
-      <c r="E15" t="n">
-        <v>2.44435076843001</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="E15" s="1">
+        <v>2.4443507684300099</v>
+      </c>
+      <c r="F15">
         <v>-0.121831153834008</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" t="n">
-        <v>9.46988004706714</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-1.85021804283286</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.11126446135347</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9.81785762967007</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16" s="1">
+        <v>9.4698800470671394</v>
+      </c>
+      <c r="D16">
+        <v>-1.8502180428328601</v>
+      </c>
+      <c r="E16">
+        <v>2.1112644613534699</v>
+      </c>
+      <c r="F16">
+        <v>9.8178576296700708</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="C17" t="n">
-        <v>-1.25972681776295</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17">
+        <v>-1.2597268177629499</v>
+      </c>
+      <c r="D17">
         <v>-0.846385446090267</v>
       </c>
-      <c r="E17" t="n">
-        <v>-1.88642713954494</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.36267224743898</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="E17">
+        <v>-1.8864271395449399</v>
+      </c>
+      <c r="F17">
+        <v>1.3626722474389801</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1">
         <v>3.15687545096239</v>
       </c>
-      <c r="D18" t="n">
-        <v>-1.49667483128354</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-1.08107955585149</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.98820825656523</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="D18">
+        <v>-1.4966748312835401</v>
+      </c>
+      <c r="E18">
+        <v>-1.0810795558514901</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2.9882082565652301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>-1.99990126303692</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>-1.99999995738725</v>
       </c>
-      <c r="E19" t="n">
-        <v>-1.79411475750794</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-1.46322953409918</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="E19">
+        <v>-1.7941147575079399</v>
+      </c>
+      <c r="F19">
+        <v>-1.4632295340991801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.131658185421657</v>
       </c>
-      <c r="D20" t="n">
-        <v>-1.14982838600463</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9.08331734495823</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="D20">
+        <v>-1.1498283860046301</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9.0833173449582301</v>
+      </c>
+      <c r="F20">
         <v>-1.99833936525647</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="n">
-        <v>22.5318577488906</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.31265007876641</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="C21" s="1">
+        <v>22.531857748890602</v>
+      </c>
+      <c r="D21">
+        <v>-0.31265007876640999</v>
+      </c>
+      <c r="E21" s="1">
         <v>19.8489512749304</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.719064918437198</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>-1.10796017318361</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="1">
         <v>2.25045915155378</v>
       </c>
-      <c r="E22" t="n">
-        <v>-0.00632672968425396</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-1.26551120879325</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="E22">
+        <v>-6.3267296842539596E-3</v>
+      </c>
+      <c r="F22">
+        <v>-1.2655112087932501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.0069286814281817</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23">
+        <v>6.9286814281817001E-3</v>
+      </c>
+      <c r="D23">
         <v>-1.97236285069857</v>
       </c>
-      <c r="E23" t="n">
-        <v>-0.318393800682635</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.720093358082281</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="E23">
+        <v>-0.31839380068263501</v>
+      </c>
+      <c r="F23">
+        <v>-0.72009335808228103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" t="n">
-        <v>4.19433237728336</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.47080746195296</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="C24" s="1">
+        <v>4.1943323772833603</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2.4708074619529601</v>
+      </c>
+      <c r="E24">
         <v>-1.97391888248666</v>
       </c>
-      <c r="F24" t="n">
-        <v>5.3302413255163</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="F24" s="1">
+        <v>5.3302413255163001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.567125468243319</v>
       </c>
-      <c r="D25" t="n">
-        <v>-1.99658499904066</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.52156367715411</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.86061423272678</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="D25">
+        <v>-1.9965849990406599</v>
+      </c>
+      <c r="E25">
+        <v>2.5215636771541101</v>
+      </c>
+      <c r="F25">
+        <v>-1.8606142327267801</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.151758205877655</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="C26">
+        <v>0.15175820587765501</v>
+      </c>
+      <c r="D26">
         <v>-1.84587446675615</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.690462083704318</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-1.0028882486137</v>
+      <c r="E26">
+        <v>0.69046208370431805</v>
+      </c>
+      <c r="F26">
+        <v>-1.0028882486137001</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>